--- a/habit_tracking_forms/002_dietary_habits_and_frequency_survey--habit_tracking_forms.xlsx
+++ b/habit_tracking_forms/002_dietary_habits_and_frequency_survey--habit_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How often do you eat</t>
+          <t>Breakfast, Lunch, and Dinner Frequency</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Do you have any food allergies</t>
+          <t>Food Allergies</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What do you eat</t>
+          <t>Types of Food Eaten</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Fruit and Vegetable Frequency</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How often do you eat certain foods</t>
+          <t>Meat and Fish Frequency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Do you eat certain foods</t>
+          <t>Time of Eating</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>When do you eat</t>
+          <t>Time Spent on Food Preparation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Do you eat when</t>
+          <t>Eating Out Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Leftovers Frequency</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How much time do you spend on food</t>
+          <t>Favorite Food</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,310 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How often do you eat</t>
+          <t>Eating Frequency</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>section_12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>section_13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>section_14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>section_15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>section_16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>section_17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>section_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>section_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>section_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Do you eat</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>section_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Do you eat</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>section_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>section_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>section_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How often do you eat</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Breakfast</t>
         </is>
       </c>
     </row>
@@ -1148,29 +849,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>section_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dinner</t>
         </is>
       </c>
     </row>
@@ -1182,29 +883,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_have_food_allergies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I have food allergies</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>section_3_choices</t>
+          <t>section_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_do_not_have_food_allergies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I do not have food allergies</t>
         </is>
       </c>
     </row>
@@ -1216,692 +917,488 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>meat_and_fish</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Meat and fish</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>section_4_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fruits_and_vegetables</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fruits and vegetables</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>section_4_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>grains</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Grains</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>section_5_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>section_5_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>section_6_choices</t>
+          <t>section_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>section_6_choices</t>
+          <t>section_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>section_7_choices</t>
+          <t>section_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>section_7_choices</t>
+          <t>section_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>section_8_choices</t>
+          <t>section_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>section_8_choices</t>
+          <t>section_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>section_9_choices</t>
+          <t>section_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>section_9_choices</t>
+          <t>section_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>section_11_choices</t>
+          <t>section_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>section_11_choices</t>
+          <t>section_6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>section_12_choices</t>
+          <t>section_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>section_12_choices</t>
+          <t>section_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>all_day</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>All day</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>section_13_choices</t>
+          <t>section_8_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>section_13_choices</t>
+          <t>section_8_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>section_14_choices</t>
+          <t>section_8_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>section_14_choices</t>
+          <t>section_8_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>section_15_choices</t>
+          <t>section_9_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>section_15_choices</t>
+          <t>section_9_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>section_16_choices</t>
+          <t>section_9_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>section_16_choices</t>
+          <t>section_9_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>section_17_choices</t>
+          <t>section_11_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>section_17_choices</t>
+          <t>section_11_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>section_18_choices</t>
+          <t>section_11_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>section_18_choices</t>
+          <t>section_11_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>section_19_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>section_19_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>section_20_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>section_20_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>section_21_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>section_21_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>section_22_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>section_22_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>section_23_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>section_23_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>section_24_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>section_24_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
